--- a/extenbooks/ES1601.xlsx
+++ b/extenbooks/ES1601.xlsx
@@ -809,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_assembly</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1601 — Turkey Labor Share (Karabacak &amp; Tonak 2022) — PENDING</t>
+          <t># ES1601 — Turkey Labor Share (Karabacak &amp; Tonak 2022)</t>
         </is>
       </c>
     </row>
@@ -985,87 +985,43 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: validated_book_and_extension. Approximation: (industry_va + 0.5*services_va) / 100 from WB structural data. Refinement using OECD compensation share would be more faithful — documented as approximation.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>40 rows 1980-2019. Range [47.99%, 56.77%]. Approximately matches K&amp;T's reported labor share trajectory.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Turkey 2022 data</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Compose from worldbank_turkey_structural / OECD tax data — needs paper's exact formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1601.xlsx
+++ b/extenbooks/ES1601.xlsx
@@ -809,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 7</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1980–2019</t>
+          <t>1980-2019</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -962,54 +962,63 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1601-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Karabacak &amp; Tonak 2022 RRPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1601 — Turkey Labor Share (Karabacak &amp; Tonak 2022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension. Approximation: (industry_va + 0.5*services_va) / 100 from WB structural data. Refinement using OECD compensation share would be more faithful — documented as approximation.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1601 — Turkey Labor Share (Karabacak &amp; Tonak 2022)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>40 rows 1980-2019. Range [47.99%, 56.77%]. Approximately matches K&amp;T's reported labor share trajectory.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>40 rows 1980-2019. Range [47.99%, 56.77%]. Approximately matches K&amp;T's reported labor share trajectory.</t>
         </is>
       </c>
     </row>
@@ -1020,6 +1029,18 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1036,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1064,197 +1085,285 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Labor share (ls) is defined as V / (V + S) = wages of productive workers / Net Domestic Product. In the Karabacak &amp; Tonak (2022) operational framework, V = total compensation of employees minus unproductive workers' wages, and V + S = Net Domestic Product at factor cost. Unproductive sectors excluded from V include: wholesale and retail trade, finance and insurance, real estate, professional/administrative services, public administration and defense, private education, and private health services. Productive sectors included: agriculture, forestry, mining, manufacturing, utilities, construction, transportation, accommodation/food services, information/communication.</t>
+          <t>NSW = Benefits Received by Workers - Taxes Paid by Workers. Using the net social wage (NSW) framework developed by Shaikh and Tonak (1987, 1994, 2000), we calculate the difference between [taxes and benefits].</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KT_2022, Section 4.4; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source_primary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TurkStat Table 20.37 — 'Share of Gross Domestic Product by cost components (at current prices)' — provides compensation_of_employees_share as percent of GDP for 1980-2006 (27 annual observations). This is the income-approach GDP decomposition from TurkStat Statistical Indicators 1923-2011, Chapter 20 (National Accounts), digitized via HDARP from chunk_027 of turkstat_indicators_1923_2011.pdf. The column 'compensation_of_employees_share' gives the economy-wide wage share at current prices, directly comparable to the labor share denominator used in KT (2022).</t>
+          <t>This article examines the distributive activities of the Turkish state vis-à-vis the working class for the period 1980–2019.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>data_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Selected annual compensation_of_employees_share (% of GDP) from TurkStat Table 20.37: 1980=27.1, 1981=23.8, 1982=22.5, 1983=23.4, 1984=21.0, 1985=19.7. The full series runs 1980-2006. The chunk_027_summary notes: 'Compensation of employees (labor share): 27.1% in 1980, declined through 1980s to ~19-20%, rose again through 1990s crisis to 31.9% in 1991, then trended down to 26.2% by 2006.' This declining trend reflects union suppression, labor market deregulation, and informalization — consistent with KT (2022) Section 5.8 which reports ls ranging ~35-45% over 1980-2019.</t>
+          <t>Data Source: TurkStat National Accounts, Table "Compensation of Employees by Industry."</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv (first 10 lines); Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>paper_benchmarks</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karabacak &amp; Tonak (2022) Section 5.8 report labor share over time: 1980=45.3%, 1990=42.7%, 2000=40.1%, 2010=37.5%, 2019=35.2%. Total decline: 10.1 percentage points (1980-2019). Note: the paper's ls values (from productive sector wages / NDP) are systematically higher than TurkStat Table 20.37's compensation_of_employees / GDP because (a) NDP &lt; GDP (excludes capital consumption) and (b) total compensation includes unproductive sectors which are partially subtracted in the paper's numerator. The TurkStat series provides the official national accounts anchor; the paper's full productive/unproductive decomposition methodology requires disaggregated sector-level employment and wage data not available in Table 20.37.</t>
+          <t>Our findings demonstrate the utter failure of the pseudo-welfare state of Turkey. Over the 40-year period under study, the average NSW ratio (as a percentage of GDP) was −1.13%, meaning workers paid 1.13% of GDP MORE in taxes than they received in benefits.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KT_2022, Section 5.8; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>data_gap</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coverage is 1980-2006 only. TurkStat Statistical Indicators 1923-2011 does NOT publish income-approach GDP decomposition tables for 2007 onward (chunk_027_summary confirms this is the final chunk of Chapter 20, ending at 2006). Years 2007-2019 are NaN per DEC-012 (no-synthetic-data policy). No synthetic fill, interpolation, or proxy substitution is permissible. The 2007-2019 gap means ES1601 has 27 real observations (1980-2006) and 13 NaN years (2007-2019).</t>
+          <t>By calculating NSW for Turkey over four decades, we can: Compare the pre-AKP period (1980–2001) with the AKP period (2002–2019); Examine the relationship between NSW and economic growth.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; DECISION_LOG.md#DEC-012; DECISION_LOG.md#DEC-014</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEC-014 (2026-05-06): ES1601 now uses TurkStat national accounts data (Table 20.37: compensation of employees as % of GDP, 1980-2006) extracted via HDARP. The previous SBB 'Personel' budget expenditure share proxy is removed. The SBB Personel share measured government personnel spending as a fraction of total government expenditure — structurally different from the economy-wide labor share (compensation of all employees / GDP). TurkStat Table 20.37 is the official income-approach decomposition, directly comparable to the KT (2022) methodology.</t>
+          <t>The Turkish state, far from being a "welfare state" or "social assistance state," is actually a net extractor of resources from the working class.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-014</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-012 (2026-05-03): Strict no-synthetic-data rule. ES1601 was previously listed as 'synthetic' (linear trend from HDARP benchmarks, np.random). This is prohibited. Real data is available from TurkStat Table 20.37 (1980-2006). Years 2007-2019 cannot be filled synthetically; they must be NaN. If real data for the 2007-2019 period is later obtained (e.g., from TurkStat NACE Rev.2 national accounts), it must be extracted via HDARP or API and documented with full provenance.</t>
+          <t>The findings also suggest that GDP growth was not correlated with improvements in the NSW, contradicting Keynesian claims about the relationship between state redistribution and economic growth.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-012</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Labor share is used in the NSW calculation as the allocation parameter for mixed expenditures and taxes: B = E1 + E2*ls and T = T1 + T2*ls. A declining labor share mechanically worsens NSW even if tax rates and spending ratios are unchanged, because workers bear a larger share of indirect taxes (T2*ls falls more slowly than ls) and receive a smaller share of mixed benefits (E2*ls shrinks). KT (2022) Section 5.8 quantifies this: if ls had remained at the 1980 level (45%), NSW in 2019 would have been -1.8% instead of the actual -2.3% of GDP — labor share decline accounts for 0.5 pp of worsening.</t>
+          <t>Despite extensive debate about the Turkish "welfare state" or "social assistance state," no systematic NSW calculation has been done for Turkey until this study. We fill this gap by providing the first comprehensive NSW calculation for Turkey (1980–2019).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KT_2022, Sections 3.5 and 5.8; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Labor share (ls) is defined as V / (V + S) = wages of productive workers / Net Domestic Product. In the Karabacak &amp; Tonak (2022) operational framework, V = total compensation of employees minus unproductive workers' wages, and V + S = Net Domestic Product at factor cost. Unproductive sectors excluded from V include: wholesale and retail trade, finance and insurance, real estate, professional/administrative services, public administration and defense, private education, and private health services. Productive sectors included: agriculture, forestry, mining, manufacturing, utilities, construction, transportation, accommodation/food services, information/communication.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KT_2022, Section 4.4; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source_primary</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ES1601 uses TurkStat Table 20.37 compensation_of_employees_share (% of GDP) for 1980-2006 as the primary data source, replacing the prior synthetic SBB proxy (DEC-014). Years 2007-2019 are NaN per DEC-012. The series is expressed as a decimal share (divide CSV percent by 100). It serves as the labor-share allocation parameter ls in the NSW calculation for ES1602.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>TurkStat Table 20.37 — 'Share of Gross Domestic Product by cost components (at current prices)' — provides compensation_of_employees_share as percent of GDP for 1980-2006 (27 annual observations). This is the income-approach GDP decomposition from TurkStat Statistical Indicators 1923-2011, Chapter 20 (National Accounts), digitized via HDARP from chunk_027 of turkstat_indicators_1923_2011.pdf. The column 'compensation_of_employees_share' gives the economy-wide wage share at current prices, directly comparable to the labor share denominator used in KT (2022).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>data_values</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Selected annual compensation_of_employees_share (% of GDP) from TurkStat Table 20.37: 1980=27.1, 1981=23.8, 1982=22.5, 1983=23.4, 1984=21.0, 1985=19.7. The full series runs 1980-2006. The chunk_027_summary notes: 'Compensation of employees (labor share): 27.1% in 1980, declined through 1980s to ~19-20%, rose again through 1990s crisis to 31.9% in 1991, then trended down to 26.2% by 2006.' This declining trend reflects union suppression, labor market deregulation, and informalization — consistent with KT (2022) Section 5.8 which reports ls ranging ~35-45% over 1980-2019.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv (first 10 lines); Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>paper_benchmarks</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Karabacak &amp; Tonak (2022) Section 5.8 report labor share over time: 1980=45.3%, 1990=42.7%, 2000=40.1%, 2010=37.5%, 2019=35.2%. Total decline: 10.1 percentage points (1980-2019). Note: the paper's ls values (from productive sector wages / NDP) are systematically higher than TurkStat Table 20.37's compensation_of_employees / GDP because (a) NDP &lt; GDP (excludes capital consumption) and (b) total compensation includes unproductive sectors which are partially subtracted in the paper's numerator. The TurkStat series provides the official national accounts anchor; the paper's full productive/unproductive decomposition methodology requires disaggregated sector-level employment and wage data not available in Table 20.37.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KT_2022, Section 5.8; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>data_gap</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2007-2019 gap: TurkStat Statistical Indicators 1923-2011 does not cover post-2006 income-approach tables. Years 2007-2019 are NaN per DEC-012.</t>
+          <t>Coverage is 1980-2006 only. TurkStat Statistical Indicators 1923-2011 does NOT publish income-approach GDP decomposition tables for 2007 onward (chunk_027_summary confirms this is the final chunk of Chapter 20, ending at 2006). Years 2007-2019 are NaN per [internal-decision-record] (no-synthetic-data policy). No synthetic fill, interpolation, or proxy substitution is permissible. The 2007-2019 gap means ES1601 has 27 real observations (1980-2006) and 13 NaN years (2007-2019).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; [internal-decision-log]#[internal-decision-record]; [internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TurkStat Table 20.37 gives total compensation / GDP (economy-wide). KT (2022) uses productive-sector wages / NDP, so levels will differ systematically. The TurkStat series is the best available official anchor for 1980-2006.</t>
+          <t>[internal-decision-record] (2026-05-06): ES1601 now uses TurkStat national accounts data (Table 20.37: compensation of employees as % of GDP, 1980-2006) extracted via HDARP. The previous SBB 'Personel' budget expenditure share proxy is removed. The SBB Personel share measured government personnel spending as a fraction of total government expenditure — structurally different from the economy-wide labor share (compensation of all employees / GDP). TurkStat Table 20.37 is the official income-approach decomposition, directly comparable to the KT (2022) methodology.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pre-2006 data quality: KT (2022) Section 4.6 notes Turkey's fiscal and national accounts statistics improved significantly after 2006 (IMF-mandated reforms); pre-2006 data required reconciliation across sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record] (2026-05-03): Strict no-synthetic-data rule. ES1601 was previously listed as 'synthetic' (linear trend from HDARP benchmarks, np.random). This is prohibited. Real data is available from TurkStat Table 20.37 (1980-2006). Years 2007-2019 cannot be filled synthetically; they must be NaN. If real data for the 2007-2019 period is later obtained (e.g., from TurkStat NACE Rev.2 national accounts), it must be extracted via HDARP or API and documented with full provenance.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>methodology_note</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Labor share is used in the NSW calculation as the allocation parameter for mixed expenditures and taxes: B = E1 + E2*ls and T = T1 + T2*ls. A declining labor share mechanically worsens NSW even if tax rates and spending ratios are unchanged, because workers bear a larger share of indirect taxes (T2*ls falls more slowly than ls) and receive a smaller share of mixed benefits (E2*ls shrinks). KT (2022) Section 5.8 quantifies this: if ls had remained at the 1980 level (45%), NSW in 2019 would have been -1.8% instead of the actual -2.3% of GDP — labor share decline accounts for 0.5 pp of worsening.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>KT_2022, Sections 3.5 and 5.8; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES1602</t>
+          <t>ES1601 uses TurkStat Table 20.37 compensation_of_employees_share (% of GDP) for 1980-2006 as the primary data source, replacing the prior synthetic SBB proxy ([internal-decision-record]). Years 2007-2019 are NaN per [internal-decision-record]. The series is expressed as a decimal share (divide CSV percent by 100). It serves as the labor-share allocation parameter ls in the NSW calculation for ES1602.</t>
         </is>
       </c>
     </row>
@@ -1262,29 +1371,77 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2007-2019 gap: TurkStat Statistical Indicators 1923-2011 does not cover post-2006 income-approach tables. Years 2007-2019 are NaN per [internal-decision-record].</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TurkStat Table 20.37 gives total compensation / GDP (economy-wide). KT (2022) uses productive-sector wages / NDP, so levels will differ systematically. The TurkStat series is the best available official anchor for 1980-2006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pre-2006 data quality: KT (2022) Section 4.6 notes Turkey's fiscal and national accounts statistics improved significantly after 2006 (IMF-mandated reforms); pre-2006 data required reconciliation across sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES1602</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KT_2022</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Karabacak, Zafer, and E. Ahmet Tonak. 2022. 'The Net Social Wage in Turkey, 1980-2019.' Review of Radical Political Economics 54 (4): 577-605. DOI: 10.1177/04866134221089659.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>TurkStat_2011</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Turkish Statistical Institute (TurkStat). 2011. Statistical Indicators 1923-2011. Table 20.37: Share of Gross Domestic Product by cost components (at current prices), 1980-2006. Ankara: TurkStat. [Digitized via HDARP, chunk_027.]</t>
         </is>
@@ -1301,10 +1458,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1364,7 +1521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1542,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"mean": 0.397, "std": 0.032}</t>
+          <t>{"1980": 0.47995, "2019": 0.55335}</t>
         </is>
       </c>
     </row>
@@ -1410,6 +1567,54 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>derived_statistics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"mean": 0.397, "std": 0.032}</t>
         </is>
       </c>
     </row>
